--- a/artfynd/A 37154-2025 artfynd.xlsx
+++ b/artfynd/A 37154-2025 artfynd.xlsx
@@ -675,37 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128629758</v>
+        <v>128629950</v>
       </c>
       <c r="B2" t="n">
-        <v>105612</v>
+        <v>98579</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>567707</v>
+        <v>567684</v>
       </c>
       <c r="R2" t="n">
-        <v>6457545</v>
+        <v>6457564</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -781,37 +781,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128629950</v>
+        <v>128629758</v>
       </c>
       <c r="B3" t="n">
-        <v>98572</v>
+        <v>105621</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>41</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -824,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>567684</v>
+        <v>567707</v>
       </c>
       <c r="R3" t="n">
-        <v>6457564</v>
+        <v>6457545</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -890,7 +890,7 @@
         <v>128629945</v>
       </c>
       <c r="B4" t="n">
-        <v>98572</v>
+        <v>98579</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>128629765</v>
       </c>
       <c r="B5" t="n">
-        <v>91473</v>
+        <v>91478</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128629862</v>
+        <v>128629890</v>
       </c>
       <c r="B6" t="n">
-        <v>98572</v>
+        <v>98579</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>43</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -1146,10 +1146,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>567564</v>
+        <v>567584</v>
       </c>
       <c r="R6" t="n">
-        <v>6457634</v>
+        <v>6457632</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1209,10 +1209,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128629856</v>
+        <v>128629862</v>
       </c>
       <c r="B7" t="n">
-        <v>98572</v>
+        <v>98579</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>38</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>567553</v>
+        <v>567564</v>
       </c>
       <c r="R7" t="n">
-        <v>6457644</v>
+        <v>6457634</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1315,10 +1315,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128629890</v>
+        <v>128629856</v>
       </c>
       <c r="B8" t="n">
-        <v>98572</v>
+        <v>98579</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
@@ -1358,10 +1358,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>567584</v>
+        <v>567553</v>
       </c>
       <c r="R8" t="n">
-        <v>6457632</v>
+        <v>6457644</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1421,42 +1421,41 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128629774</v>
+        <v>128629822</v>
       </c>
       <c r="B9" t="n">
-        <v>98572</v>
+        <v>91478</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1464,10 +1463,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>567674</v>
+        <v>567625</v>
       </c>
       <c r="R9" t="n">
-        <v>6457609</v>
+        <v>6457686</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1530,7 +1529,7 @@
         <v>128629762</v>
       </c>
       <c r="B10" t="n">
-        <v>91473</v>
+        <v>91478</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1632,41 +1631,42 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128629822</v>
+        <v>128629774</v>
       </c>
       <c r="B11" t="n">
-        <v>91473</v>
+        <v>98579</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1674,10 +1674,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>567625</v>
+        <v>567674</v>
       </c>
       <c r="R11" t="n">
-        <v>6457686</v>
+        <v>6457609</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1740,7 +1740,7 @@
         <v>128629757</v>
       </c>
       <c r="B12" t="n">
-        <v>91473</v>
+        <v>91478</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>128629838</v>
       </c>
       <c r="B13" t="n">
-        <v>98572</v>
+        <v>98579</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>128629824</v>
       </c>
       <c r="B14" t="n">
-        <v>92085</v>
+        <v>92090</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>128629779</v>
       </c>
       <c r="B15" t="n">
-        <v>92085</v>
+        <v>92090</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
         <v>128629865</v>
       </c>
       <c r="B16" t="n">
-        <v>92085</v>
+        <v>92090</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>128629887</v>
       </c>
       <c r="B17" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 37154-2025 artfynd.xlsx
+++ b/artfynd/A 37154-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128629950</v>
       </c>
       <c r="B2" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128629758</v>
       </c>
       <c r="B3" t="n">
-        <v>105621</v>
+        <v>105630</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>128629945</v>
       </c>
       <c r="B4" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>128629765</v>
       </c>
       <c r="B5" t="n">
-        <v>91478</v>
+        <v>91484</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>128629890</v>
       </c>
       <c r="B6" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>128629862</v>
       </c>
       <c r="B7" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>128629856</v>
       </c>
       <c r="B8" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>128629822</v>
       </c>
       <c r="B9" t="n">
-        <v>91478</v>
+        <v>91484</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         <v>128629762</v>
       </c>
       <c r="B10" t="n">
-        <v>91478</v>
+        <v>91484</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>128629774</v>
       </c>
       <c r="B11" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         <v>128629757</v>
       </c>
       <c r="B12" t="n">
-        <v>91478</v>
+        <v>91484</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>128629838</v>
       </c>
       <c r="B13" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>128629824</v>
       </c>
       <c r="B14" t="n">
-        <v>92090</v>
+        <v>92096</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>128629779</v>
       </c>
       <c r="B15" t="n">
-        <v>92090</v>
+        <v>92096</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
         <v>128629865</v>
       </c>
       <c r="B16" t="n">
-        <v>92090</v>
+        <v>92096</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 37154-2025 artfynd.xlsx
+++ b/artfynd/A 37154-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128629950</v>
       </c>
       <c r="B2" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128629758</v>
       </c>
       <c r="B3" t="n">
-        <v>105630</v>
+        <v>105642</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>128629945</v>
       </c>
       <c r="B4" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>128629765</v>
       </c>
       <c r="B5" t="n">
-        <v>91484</v>
+        <v>91486</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>128629890</v>
       </c>
       <c r="B6" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>128629862</v>
       </c>
       <c r="B7" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>128629856</v>
       </c>
       <c r="B8" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>128629822</v>
       </c>
       <c r="B9" t="n">
-        <v>91484</v>
+        <v>91486</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         <v>128629762</v>
       </c>
       <c r="B10" t="n">
-        <v>91484</v>
+        <v>91486</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>128629774</v>
       </c>
       <c r="B11" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         <v>128629757</v>
       </c>
       <c r="B12" t="n">
-        <v>91484</v>
+        <v>91486</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>128629838</v>
       </c>
       <c r="B13" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>128629824</v>
       </c>
       <c r="B14" t="n">
-        <v>92096</v>
+        <v>92098</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>128629779</v>
       </c>
       <c r="B15" t="n">
-        <v>92096</v>
+        <v>92098</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
         <v>128629865</v>
       </c>
       <c r="B16" t="n">
-        <v>92096</v>
+        <v>92098</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 37154-2025 artfynd.xlsx
+++ b/artfynd/A 37154-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128629950</v>
       </c>
       <c r="B2" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128629758</v>
       </c>
       <c r="B3" t="n">
-        <v>105642</v>
+        <v>105651</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>128629945</v>
       </c>
       <c r="B4" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>128629890</v>
       </c>
       <c r="B6" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>128629862</v>
       </c>
       <c r="B7" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>128629856</v>
       </c>
       <c r="B8" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>128629774</v>
       </c>
       <c r="B11" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>128629838</v>
       </c>
       <c r="B13" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 37154-2025 artfynd.xlsx
+++ b/artfynd/A 37154-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128629950</v>
       </c>
       <c r="B2" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128629758</v>
       </c>
       <c r="B3" t="n">
-        <v>105651</v>
+        <v>105654</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>128629945</v>
       </c>
       <c r="B4" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>128629765</v>
       </c>
       <c r="B5" t="n">
-        <v>91486</v>
+        <v>91487</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>128629890</v>
       </c>
       <c r="B6" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>128629862</v>
       </c>
       <c r="B7" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>128629856</v>
       </c>
       <c r="B8" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>128629822</v>
       </c>
       <c r="B9" t="n">
-        <v>91486</v>
+        <v>91487</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         <v>128629762</v>
       </c>
       <c r="B10" t="n">
-        <v>91486</v>
+        <v>91487</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>128629774</v>
       </c>
       <c r="B11" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         <v>128629757</v>
       </c>
       <c r="B12" t="n">
-        <v>91486</v>
+        <v>91487</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>128629838</v>
       </c>
       <c r="B13" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>128629824</v>
       </c>
       <c r="B14" t="n">
-        <v>92098</v>
+        <v>92099</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>128629779</v>
       </c>
       <c r="B15" t="n">
-        <v>92098</v>
+        <v>92099</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
         <v>128629865</v>
       </c>
       <c r="B16" t="n">
-        <v>92098</v>
+        <v>92099</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 37154-2025 artfynd.xlsx
+++ b/artfynd/A 37154-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128629950</v>
       </c>
       <c r="B2" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128629758</v>
       </c>
       <c r="B3" t="n">
-        <v>105654</v>
+        <v>105682</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>128629945</v>
       </c>
       <c r="B4" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>128629765</v>
       </c>
       <c r="B5" t="n">
-        <v>91487</v>
+        <v>91514</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>128629890</v>
       </c>
       <c r="B6" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>128629862</v>
       </c>
       <c r="B7" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>128629856</v>
       </c>
       <c r="B8" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>128629822</v>
       </c>
       <c r="B9" t="n">
-        <v>91487</v>
+        <v>91514</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         <v>128629762</v>
       </c>
       <c r="B10" t="n">
-        <v>91487</v>
+        <v>91514</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>128629774</v>
       </c>
       <c r="B11" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         <v>128629757</v>
       </c>
       <c r="B12" t="n">
-        <v>91487</v>
+        <v>91514</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>128629838</v>
       </c>
       <c r="B13" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>128629824</v>
       </c>
       <c r="B14" t="n">
-        <v>92099</v>
+        <v>92126</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>128629779</v>
       </c>
       <c r="B15" t="n">
-        <v>92099</v>
+        <v>92126</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
         <v>128629865</v>
       </c>
       <c r="B16" t="n">
-        <v>92099</v>
+        <v>92126</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>128629887</v>
       </c>
       <c r="B17" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 37154-2025 artfynd.xlsx
+++ b/artfynd/A 37154-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128629950</v>
       </c>
       <c r="B2" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128629758</v>
       </c>
       <c r="B3" t="n">
-        <v>105682</v>
+        <v>105688</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>128629945</v>
       </c>
       <c r="B4" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>128629765</v>
       </c>
       <c r="B5" t="n">
-        <v>91514</v>
+        <v>91519</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>128629890</v>
       </c>
       <c r="B6" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>128629862</v>
       </c>
       <c r="B7" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>128629856</v>
       </c>
       <c r="B8" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>128629822</v>
       </c>
       <c r="B9" t="n">
-        <v>91514</v>
+        <v>91519</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         <v>128629762</v>
       </c>
       <c r="B10" t="n">
-        <v>91514</v>
+        <v>91519</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>128629774</v>
       </c>
       <c r="B11" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         <v>128629757</v>
       </c>
       <c r="B12" t="n">
-        <v>91514</v>
+        <v>91519</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>128629838</v>
       </c>
       <c r="B13" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>128629824</v>
       </c>
       <c r="B14" t="n">
-        <v>92126</v>
+        <v>92131</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>128629779</v>
       </c>
       <c r="B15" t="n">
-        <v>92126</v>
+        <v>92131</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
         <v>128629865</v>
       </c>
       <c r="B16" t="n">
-        <v>92126</v>
+        <v>92131</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 37154-2025 artfynd.xlsx
+++ b/artfynd/A 37154-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128629950</v>
       </c>
       <c r="B2" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128629758</v>
       </c>
       <c r="B3" t="n">
-        <v>105688</v>
+        <v>105695</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>128629945</v>
       </c>
       <c r="B4" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>128629765</v>
       </c>
       <c r="B5" t="n">
-        <v>91519</v>
+        <v>91524</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>128629890</v>
       </c>
       <c r="B6" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>128629862</v>
       </c>
       <c r="B7" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>128629856</v>
       </c>
       <c r="B8" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>128629822</v>
       </c>
       <c r="B9" t="n">
-        <v>91519</v>
+        <v>91524</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         <v>128629762</v>
       </c>
       <c r="B10" t="n">
-        <v>91519</v>
+        <v>91524</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>128629774</v>
       </c>
       <c r="B11" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         <v>128629757</v>
       </c>
       <c r="B12" t="n">
-        <v>91519</v>
+        <v>91524</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>128629838</v>
       </c>
       <c r="B13" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>128629824</v>
       </c>
       <c r="B14" t="n">
-        <v>92131</v>
+        <v>92136</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>128629779</v>
       </c>
       <c r="B15" t="n">
-        <v>92131</v>
+        <v>92136</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
         <v>128629865</v>
       </c>
       <c r="B16" t="n">
-        <v>92131</v>
+        <v>92136</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 37154-2025 artfynd.xlsx
+++ b/artfynd/A 37154-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128629950</v>
       </c>
       <c r="B2" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128629758</v>
       </c>
       <c r="B3" t="n">
-        <v>105695</v>
+        <v>105699</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>128629945</v>
       </c>
       <c r="B4" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>128629765</v>
       </c>
       <c r="B5" t="n">
-        <v>91524</v>
+        <v>91528</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>128629890</v>
       </c>
       <c r="B6" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>128629862</v>
       </c>
       <c r="B7" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>128629856</v>
       </c>
       <c r="B8" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>128629822</v>
       </c>
       <c r="B9" t="n">
-        <v>91524</v>
+        <v>91528</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         <v>128629762</v>
       </c>
       <c r="B10" t="n">
-        <v>91524</v>
+        <v>91528</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>128629774</v>
       </c>
       <c r="B11" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         <v>128629757</v>
       </c>
       <c r="B12" t="n">
-        <v>91524</v>
+        <v>91528</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>128629838</v>
       </c>
       <c r="B13" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>128629824</v>
       </c>
       <c r="B14" t="n">
-        <v>92136</v>
+        <v>92140</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>128629779</v>
       </c>
       <c r="B15" t="n">
-        <v>92136</v>
+        <v>92140</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
         <v>128629865</v>
       </c>
       <c r="B16" t="n">
-        <v>92136</v>
+        <v>92140</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>128629887</v>
       </c>
       <c r="B17" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 37154-2025 artfynd.xlsx
+++ b/artfynd/A 37154-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128629950</v>
       </c>
       <c r="B2" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128629758</v>
       </c>
       <c r="B3" t="n">
-        <v>105699</v>
+        <v>105706</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>128629945</v>
       </c>
       <c r="B4" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>128629765</v>
       </c>
       <c r="B5" t="n">
-        <v>91528</v>
+        <v>91533</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>128629890</v>
       </c>
       <c r="B6" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>128629862</v>
       </c>
       <c r="B7" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>128629856</v>
       </c>
       <c r="B8" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>128629822</v>
       </c>
       <c r="B9" t="n">
-        <v>91528</v>
+        <v>91533</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         <v>128629762</v>
       </c>
       <c r="B10" t="n">
-        <v>91528</v>
+        <v>91533</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>128629774</v>
       </c>
       <c r="B11" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         <v>128629757</v>
       </c>
       <c r="B12" t="n">
-        <v>91528</v>
+        <v>91533</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>128629838</v>
       </c>
       <c r="B13" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>128629824</v>
       </c>
       <c r="B14" t="n">
-        <v>92140</v>
+        <v>92145</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>128629779</v>
       </c>
       <c r="B15" t="n">
-        <v>92140</v>
+        <v>92145</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
         <v>128629865</v>
       </c>
       <c r="B16" t="n">
-        <v>92140</v>
+        <v>92145</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>128629887</v>
       </c>
       <c r="B17" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
